--- a/ig/main/ValueSet-1.2.250.1.213.1.1.5.687.xlsx
+++ b/ig/main/ValueSet-1.2.250.1.213.1.1.5.687.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12646" uniqueCount="12641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12718" uniqueCount="12713">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20220805000000</t>
+    <t>20240731000000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,13 +63,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-05T01:00:00+02:00</t>
+    <t>2024-07-31T00:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+    <t>Agence du Numérique en Santé(ANS) -2 - 10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Description</t>
@@ -126,12 +126,6 @@
     <t>étude par un sigmoïdoscope flexible</t>
   </si>
   <si>
-    <t>18756-7</t>
-  </si>
-  <si>
-    <t>RM rachis.XXX ; compte rendu</t>
-  </si>
-  <si>
     <t>24531-6</t>
   </si>
   <si>
@@ -4884,6 +4878,36 @@
     <t>RX hanche - droite ; incidence unique</t>
   </si>
   <si>
+    <t>28012-3</t>
+  </si>
+  <si>
+    <t>étude oesophagoscopique</t>
+  </si>
+  <si>
+    <t>28018-0</t>
+  </si>
+  <si>
+    <t>étude entéroscopique</t>
+  </si>
+  <si>
+    <t>28020-6</t>
+  </si>
+  <si>
+    <t>entéroscopie à  travers une stomie</t>
+  </si>
+  <si>
+    <t>28028-9</t>
+  </si>
+  <si>
+    <t>étude anuscopique</t>
+  </si>
+  <si>
+    <t>28033-9</t>
+  </si>
+  <si>
+    <t>étude colonoscopique à  travers une stomie</t>
+  </si>
+  <si>
     <t>28561-9</t>
   </si>
   <si>
@@ -37929,13 +37953,205 @@
     <t>RX rachis dorsal ; incidence avec flexion</t>
   </si>
   <si>
+    <t>98897-2</t>
+  </si>
+  <si>
+    <t>RX pelvis et hanche - abduction gauche et rotation interne</t>
+  </si>
+  <si>
+    <t>98898-0</t>
+  </si>
+  <si>
+    <t>RX pelvis et hanche - droite</t>
+  </si>
+  <si>
+    <t>98899-8</t>
+  </si>
+  <si>
+    <t>RX poignet - droit incidence 3/4 en pronation</t>
+  </si>
+  <si>
+    <t>98900-4</t>
+  </si>
+  <si>
+    <t>RX poignet - gauche incidence 3/4 en pronation</t>
+  </si>
+  <si>
+    <t>99505-0</t>
+  </si>
+  <si>
+    <t>RX poignet - incidence postéroantérieure gauche</t>
+  </si>
+  <si>
+    <t>99506-8</t>
+  </si>
+  <si>
+    <t>RX poignet - incidence postéroantérieure droit</t>
+  </si>
+  <si>
+    <t>99507-6</t>
+  </si>
+  <si>
+    <t>RX de la hanche droite 3/4 externe de Judet</t>
+  </si>
+  <si>
+    <t>99508-4</t>
+  </si>
+  <si>
+    <t>RX de la hanche gauche 3/4 externe de Judet</t>
+  </si>
+  <si>
+    <t>99509-2</t>
+  </si>
+  <si>
+    <t>RX de la hanche gauche 3/4 interne de Judet</t>
+  </si>
+  <si>
+    <t>99510-0</t>
+  </si>
+  <si>
+    <t>RX de la hanche droite 3/4 interne de Judet</t>
+  </si>
+  <si>
+    <t>99511-8</t>
+  </si>
+  <si>
+    <t>RX.radiographie collimatée en fente incidences moelle spinale</t>
+  </si>
+  <si>
+    <t>99605-8</t>
+  </si>
+  <si>
+    <t>échographie.doppler vaisseaux du membre inférieur - gauche pour cartographie veineuse</t>
+  </si>
+  <si>
+    <t>99606-6</t>
+  </si>
+  <si>
+    <t>échographie.doppler vaisseaux du membre inférieur - droit pour cartographie veineuse</t>
+  </si>
+  <si>
+    <t>99607-4</t>
+  </si>
+  <si>
+    <t>échographie.doppler vaisseaux du membre inférieur - bilatéral pour cartographie veineuse</t>
+  </si>
+  <si>
+    <t>99608-2</t>
+  </si>
+  <si>
+    <t>angioIRM des vaisseaux sousclaviers - bilatéral sans et avec contraste IV</t>
+  </si>
+  <si>
+    <t>99609-0</t>
+  </si>
+  <si>
+    <t>angioIRM de l'aorte thoracique avec contraste IV</t>
+  </si>
+  <si>
+    <t>99610-8</t>
+  </si>
+  <si>
+    <t>CT Abdomen et Pelvis avec contraste per os</t>
+  </si>
+  <si>
+    <t>99611-6</t>
+  </si>
+  <si>
+    <t>angioIRM des vaisseaux abdominaux et vaisseaux du pelvis sans contraste</t>
+  </si>
+  <si>
+    <t>99612-4</t>
+  </si>
+  <si>
+    <t>scanner coeur sans contraste</t>
+  </si>
+  <si>
+    <t>99613-2</t>
+  </si>
+  <si>
+    <t>scanner du coeur sans et avec contraste IV</t>
+  </si>
+  <si>
+    <t>99628-0</t>
+  </si>
+  <si>
+    <t>scanner Cou+Thorax+Abdomen+Pelvis</t>
+  </si>
+  <si>
+    <t>99629-8</t>
+  </si>
+  <si>
+    <t>scanner Cou+Thorax+Abdomen+Pelvis sans contraste</t>
+  </si>
+  <si>
+    <t>99630-6</t>
+  </si>
+  <si>
+    <t>scanner Cou+Thorax+Abdomen+Pelvis sans et avec contraste IV</t>
+  </si>
+  <si>
+    <t>99631-4</t>
+  </si>
+  <si>
+    <t>CT cone beam articulation temporomandibulaire - bilatérale</t>
+  </si>
+  <si>
+    <t>99632-2</t>
+  </si>
+  <si>
+    <t>CT cone beam articulation temporomandibulaire sans et avec contraste IV</t>
+  </si>
+  <si>
+    <t>99633-0</t>
+  </si>
+  <si>
+    <t>CT Cone beam des dents</t>
+  </si>
+  <si>
+    <t>99702-3</t>
+  </si>
+  <si>
+    <t>tractographie par résonnance magnétique du cerveau</t>
+  </si>
+  <si>
+    <t>99703-1</t>
+  </si>
+  <si>
+    <t>résonnance magnétique de perfusion du cerveau</t>
+  </si>
+  <si>
+    <t>99704-9</t>
+  </si>
+  <si>
+    <t>résonnance magnétique du cerveau pour cartographie d'accident vasculaire cérébral</t>
+  </si>
+  <si>
+    <t>99705-6</t>
+  </si>
+  <si>
+    <t>résonnance magnétique du cerveau pour cartographie de crises comitiales</t>
+  </si>
+  <si>
+    <t>99826-0</t>
+  </si>
+  <si>
+    <t>échographie.A-scan oeil</t>
+  </si>
+  <si>
+    <t>99827-8</t>
+  </si>
+  <si>
+    <t>échographie.élastographie du sein</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
     <t>System URI</t>
   </si>
   <si>
-    <t>urn:oid:2.16.840.1.113883.6.1</t>
+    <t>http://loinc.org</t>
   </si>
 </sst>
 </file>
@@ -38191,7 +38407,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6310"/>
+  <dimension ref="A1:B6346"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -76003,39 +76219,39 @@
         <v>9473</v>
       </c>
       <c r="B4726" t="s" s="2">
-        <v>7664</v>
+        <v>9474</v>
       </c>
     </row>
     <row r="4727">
       <c r="A4727" t="s" s="2">
-        <v>9474</v>
+        <v>9475</v>
       </c>
       <c r="B4727" t="s" s="2">
-        <v>9475</v>
+        <v>9476</v>
       </c>
     </row>
     <row r="4728">
       <c r="A4728" t="s" s="2">
-        <v>9476</v>
+        <v>9477</v>
       </c>
       <c r="B4728" t="s" s="2">
-        <v>9477</v>
+        <v>9478</v>
       </c>
     </row>
     <row r="4729">
       <c r="A4729" t="s" s="2">
-        <v>9478</v>
+        <v>9479</v>
       </c>
       <c r="B4729" t="s" s="2">
-        <v>9479</v>
+        <v>9480</v>
       </c>
     </row>
     <row r="4730">
       <c r="A4730" t="s" s="2">
-        <v>9480</v>
+        <v>9481</v>
       </c>
       <c r="B4730" t="s" s="2">
-        <v>9481</v>
+        <v>7672</v>
       </c>
     </row>
     <row r="4731">
@@ -88667,15 +88883,303 @@
         <v>12638</v>
       </c>
       <c r="B6309" t="s" s="2">
-        <v>12638</v>
+        <v>12639</v>
       </c>
     </row>
     <row r="6310">
       <c r="A6310" t="s" s="2">
-        <v>12639</v>
+        <v>12640</v>
       </c>
       <c r="B6310" t="s" s="2">
-        <v>12640</v>
+        <v>12641</v>
+      </c>
+    </row>
+    <row r="6311">
+      <c r="A6311" t="s" s="2">
+        <v>12642</v>
+      </c>
+      <c r="B6311" t="s" s="2">
+        <v>12643</v>
+      </c>
+    </row>
+    <row r="6312">
+      <c r="A6312" t="s" s="2">
+        <v>12644</v>
+      </c>
+      <c r="B6312" t="s" s="2">
+        <v>12645</v>
+      </c>
+    </row>
+    <row r="6313">
+      <c r="A6313" t="s" s="2">
+        <v>12646</v>
+      </c>
+      <c r="B6313" t="s" s="2">
+        <v>12647</v>
+      </c>
+    </row>
+    <row r="6314">
+      <c r="A6314" t="s" s="2">
+        <v>12648</v>
+      </c>
+      <c r="B6314" t="s" s="2">
+        <v>12649</v>
+      </c>
+    </row>
+    <row r="6315">
+      <c r="A6315" t="s" s="2">
+        <v>12650</v>
+      </c>
+      <c r="B6315" t="s" s="2">
+        <v>12651</v>
+      </c>
+    </row>
+    <row r="6316">
+      <c r="A6316" t="s" s="2">
+        <v>12652</v>
+      </c>
+      <c r="B6316" t="s" s="2">
+        <v>12653</v>
+      </c>
+    </row>
+    <row r="6317">
+      <c r="A6317" t="s" s="2">
+        <v>12654</v>
+      </c>
+      <c r="B6317" t="s" s="2">
+        <v>12655</v>
+      </c>
+    </row>
+    <row r="6318">
+      <c r="A6318" t="s" s="2">
+        <v>12656</v>
+      </c>
+      <c r="B6318" t="s" s="2">
+        <v>12657</v>
+      </c>
+    </row>
+    <row r="6319">
+      <c r="A6319" t="s" s="2">
+        <v>12658</v>
+      </c>
+      <c r="B6319" t="s" s="2">
+        <v>12659</v>
+      </c>
+    </row>
+    <row r="6320">
+      <c r="A6320" t="s" s="2">
+        <v>12660</v>
+      </c>
+      <c r="B6320" t="s" s="2">
+        <v>12661</v>
+      </c>
+    </row>
+    <row r="6321">
+      <c r="A6321" t="s" s="2">
+        <v>12662</v>
+      </c>
+      <c r="B6321" t="s" s="2">
+        <v>12663</v>
+      </c>
+    </row>
+    <row r="6322">
+      <c r="A6322" t="s" s="2">
+        <v>12664</v>
+      </c>
+      <c r="B6322" t="s" s="2">
+        <v>12665</v>
+      </c>
+    </row>
+    <row r="6323">
+      <c r="A6323" t="s" s="2">
+        <v>12666</v>
+      </c>
+      <c r="B6323" t="s" s="2">
+        <v>12667</v>
+      </c>
+    </row>
+    <row r="6324">
+      <c r="A6324" t="s" s="2">
+        <v>12668</v>
+      </c>
+      <c r="B6324" t="s" s="2">
+        <v>12669</v>
+      </c>
+    </row>
+    <row r="6325">
+      <c r="A6325" t="s" s="2">
+        <v>12670</v>
+      </c>
+      <c r="B6325" t="s" s="2">
+        <v>12671</v>
+      </c>
+    </row>
+    <row r="6326">
+      <c r="A6326" t="s" s="2">
+        <v>12672</v>
+      </c>
+      <c r="B6326" t="s" s="2">
+        <v>12673</v>
+      </c>
+    </row>
+    <row r="6327">
+      <c r="A6327" t="s" s="2">
+        <v>12674</v>
+      </c>
+      <c r="B6327" t="s" s="2">
+        <v>12675</v>
+      </c>
+    </row>
+    <row r="6328">
+      <c r="A6328" t="s" s="2">
+        <v>12676</v>
+      </c>
+      <c r="B6328" t="s" s="2">
+        <v>12677</v>
+      </c>
+    </row>
+    <row r="6329">
+      <c r="A6329" t="s" s="2">
+        <v>12678</v>
+      </c>
+      <c r="B6329" t="s" s="2">
+        <v>12679</v>
+      </c>
+    </row>
+    <row r="6330">
+      <c r="A6330" t="s" s="2">
+        <v>12680</v>
+      </c>
+      <c r="B6330" t="s" s="2">
+        <v>12681</v>
+      </c>
+    </row>
+    <row r="6331">
+      <c r="A6331" t="s" s="2">
+        <v>12682</v>
+      </c>
+      <c r="B6331" t="s" s="2">
+        <v>12683</v>
+      </c>
+    </row>
+    <row r="6332">
+      <c r="A6332" t="s" s="2">
+        <v>12684</v>
+      </c>
+      <c r="B6332" t="s" s="2">
+        <v>12685</v>
+      </c>
+    </row>
+    <row r="6333">
+      <c r="A6333" t="s" s="2">
+        <v>12686</v>
+      </c>
+      <c r="B6333" t="s" s="2">
+        <v>12687</v>
+      </c>
+    </row>
+    <row r="6334">
+      <c r="A6334" t="s" s="2">
+        <v>12688</v>
+      </c>
+      <c r="B6334" t="s" s="2">
+        <v>12689</v>
+      </c>
+    </row>
+    <row r="6335">
+      <c r="A6335" t="s" s="2">
+        <v>12690</v>
+      </c>
+      <c r="B6335" t="s" s="2">
+        <v>12691</v>
+      </c>
+    </row>
+    <row r="6336">
+      <c r="A6336" t="s" s="2">
+        <v>12692</v>
+      </c>
+      <c r="B6336" t="s" s="2">
+        <v>12693</v>
+      </c>
+    </row>
+    <row r="6337">
+      <c r="A6337" t="s" s="2">
+        <v>12694</v>
+      </c>
+      <c r="B6337" t="s" s="2">
+        <v>12695</v>
+      </c>
+    </row>
+    <row r="6338">
+      <c r="A6338" t="s" s="2">
+        <v>12696</v>
+      </c>
+      <c r="B6338" t="s" s="2">
+        <v>12697</v>
+      </c>
+    </row>
+    <row r="6339">
+      <c r="A6339" t="s" s="2">
+        <v>12698</v>
+      </c>
+      <c r="B6339" t="s" s="2">
+        <v>12699</v>
+      </c>
+    </row>
+    <row r="6340">
+      <c r="A6340" t="s" s="2">
+        <v>12700</v>
+      </c>
+      <c r="B6340" t="s" s="2">
+        <v>12701</v>
+      </c>
+    </row>
+    <row r="6341">
+      <c r="A6341" t="s" s="2">
+        <v>12702</v>
+      </c>
+      <c r="B6341" t="s" s="2">
+        <v>12703</v>
+      </c>
+    </row>
+    <row r="6342">
+      <c r="A6342" t="s" s="2">
+        <v>12704</v>
+      </c>
+      <c r="B6342" t="s" s="2">
+        <v>12705</v>
+      </c>
+    </row>
+    <row r="6343">
+      <c r="A6343" t="s" s="2">
+        <v>12706</v>
+      </c>
+      <c r="B6343" t="s" s="2">
+        <v>12707</v>
+      </c>
+    </row>
+    <row r="6344">
+      <c r="A6344" t="s" s="2">
+        <v>12708</v>
+      </c>
+      <c r="B6344" t="s" s="2">
+        <v>12709</v>
+      </c>
+    </row>
+    <row r="6345">
+      <c r="A6345" t="s" s="2">
+        <v>12710</v>
+      </c>
+      <c r="B6345" t="s" s="2">
+        <v>12710</v>
+      </c>
+    </row>
+    <row r="6346">
+      <c r="A6346" t="s" s="2">
+        <v>12711</v>
+      </c>
+      <c r="B6346" t="s" s="2">
+        <v>12712</v>
       </c>
     </row>
   </sheetData>
